--- a/web/files/九龙-何文田-耀爵台.xlsx
+++ b/web/files/九龙-何文田-耀爵台.xlsx
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>65500000</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>32948</v>
+        <v>32981</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -1456,9 +1456,9 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>- | 1988呎 (4+房)
+          <t>- | 1986呎 (4+房)
 $6550万
-$32,948/呎
+$32,981/呎
 (18年-08月-28日)</t>
         </is>
       </c>
